--- a/NSAT_QuestionBank_Template.xlsx
+++ b/NSAT_QuestionBank_Template.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Test Config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +28,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
       <i val="1"/>
-      <color rgb="007F6000"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002C6B42"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002C6B42"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008A6516"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -49,26 +74,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
+        <fgColor rgb="002C6B42"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F0F4F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F7FB"/>
-        <bgColor rgb="00F2F7FB"/>
+        <fgColor rgb="00FFF8E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,25 +119,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,23 +525,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>type</t>
@@ -559,99 +601,107 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>mcq or shortanswer</t>
+          <t>multipleChoice
+or shortAnswer</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>e.g. B.Tech, BBA, B.Sc</t>
+          <t>e.g. btech</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>e.g. Physics, Aptitude</t>
+          <t>e.g. Physics</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Type the full question here...</t>
+          <t>Full question text</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Option A text</t>
+          <t>Option A text
+(MCQ only)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Option B text</t>
+          <t>Option B text
+(MCQ only)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Option C text</t>
+          <t>Option C text
+(MCQ only)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Option D text</t>
+          <t>Option D text
+(MCQ only)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>A / B / C / D (or leave blank for short answer)</t>
+          <t>A, B, C, or D
+(MCQ only)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Only for short answer (e.g. 100)</t>
+          <t>Min words
+(short answer)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Only for short answer (e.g. 150)</t>
+          <t>Max words
+(short answer)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>multipleChoice</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>soahs_ug</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>What is the value of (12 × 15) ÷ 6?</t>
+          <t>Biology - Cell Biology</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Which cell organelle is commonly referred to as the "powerhouse of the cell"?</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Ribosome</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Mitochondrion</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Golgi apparatus</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Lysosome</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -663,90 +713,2438 @@
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>shortanswer</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Essay</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Genetics</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Explain the importance of data structures in computer science.</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>What is the typical phenotypic ratio of a Mendelian monohybrid cross in the F2 generation?</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>9:3:3:1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>01:02:01</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>9:7</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>mcq</t>
+          <t>multipleChoice</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>soahs_ug</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Business Awareness</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Which of the following is NOT a type of market structure?</t>
+          <t>Biology - Plant Physiology</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>During photosynthesis, the light-dependent reactions take place within the:</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Monopoly</t>
+          <t>Stroma</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Oligopoly</t>
+          <t>Thylakoid membrane</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Monopsony</t>
+          <t>Cytoplasm</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Inflation</t>
+          <t>Mitochondrial matrix</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Human Physiology</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Which of the following structures acts as the natural pacemaker of the human heart?</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Atrioventricular (AV) Node</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Purkinje fibers</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Sinoatrial (SA) Node</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Bundle of His</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Human Physiology</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>The structural and functional unit of the human kidney is the:</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Neuron</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Nephron</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Nephridia</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Alveolus</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Human Physiology</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Which part of the human brain is primarily responsible for regulating voluntary muscular movements, balance, and posture?</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Cerebrum</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Cerebellum</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Medulla Oblongata</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Hypothalamus</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Biomolecules</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Amino acids are the basic building blocks of which type of biomolecule?</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Carbohydrates</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Lipids</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Proteins</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Nucleic acids</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Ecology</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>In an ecological food chain, primary consumers occupy which trophic level?</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>First trophic level</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Second trophic level</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Third trophic level</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Fourth trophic level</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Biotechnology</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Which enzymes are commonly referred to as "molecular scissors" in recombinant DNA technology?</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>DNA ligases</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Restriction endonucleases</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>DNA polymerases</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Helicases</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Evolution</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Organs that share a similar basic anatomical structure and embryonic origin but perform different functions are called:</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Analogous organs</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Homologous organs</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Vestigial organs</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Atavistic organs</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Plant Reproduction</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>The phenomenon of "double fertilization" is a reproductive characteristic unique to:</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Bryophytes</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Pteridophytes</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Gymsomperms</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Angiosperms</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Human Reproduction</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>In humans, fertilization of the ovum by the sperm typically occurs in which specific part of the female reproductive tract?</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Uterus</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Cervix</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Ampulla of the Fallopian tube</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Vagina</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Cell Division</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>During which stage of mitosis do chromosomes align perfectly along the equatorial plate of the cell?</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Prophase</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Metaphase</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Anaphase</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Telophase</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Industrial Microbiology</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Which microorganism is widely utilized in the commercial baking and brewing industries?</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Lactobacillus</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Saccharomyces cerevisiae</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Aspergillus niger</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Penicillium notatum</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Plant Kingdom</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Plant species that lack vascular tissue and are frequently described as the "amphibians of the plant kingdom" belong to:</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Thallophytes</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Bryophytes</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Pteridophytes</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Gymnosperms</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Animal Kingdom</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Which of the following is a defining characteristic feature of the phylum Arthropoda?</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Water vascular system</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Jointed appendages</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Cnidocytes</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Radula</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Human Physiology</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Which hormone is secreted by the beta cells of the pancreas to facilitate glucose uptake and lower blood sugar levels?</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Glucagon</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Insulin</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Adrenaline</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Thyroxine</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Molecular Genetics</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Which of the following nitrogenous bases is a purine found in DNA molecules?</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Cytosine</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Thymine</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Uracil</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Adenine</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Human Health</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>The immunity acquired by an individual immediately after receiving a standardized vaccine dose is an example of:</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Active artificial immunity</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Passive artificial immunity</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Active natural immunity</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Passive natural immunity</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Biology - Environmental Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Which greenhouse gas is currently the largest contributor to anthropogenic global warming?</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Methane</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Nitrous oxide</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Carbon dioxide</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Ozone</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Units &amp; Measurements</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>What is the fundamental SI unit of force?</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Joule</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Watt</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Newton</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Pascal</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Electrostatics</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>According to Coulomb's Law, if the distance between two fixed point charges is doubled, the electrostatic force between them becomes:</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Doubled</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Halved</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Four times</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>One-fourth</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Current Electricity</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>The electrical resistance of a uniform metallic conductor is:</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Directly proportional to its length and inversely proportional to its cross-sectional area</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Inversely proportional to its length and directly proportional to its cross-sectional area</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Directly proportional to both its length and cross-sectional area</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Independent of both its length and cross-sectional area</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Magnetic Effects</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>A charged particle moves through a uniform magnetic field. The magnetic force acting on the particle is at its maximum when the angle between its velocity vector and the magnetic field lines is:</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>0°</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>45°</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>90°</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>180°</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Ray Optics</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>The twinkling of stars observed in the night sky is primarily caused by which optical phenomenon?</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Total internal reflection</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Atmospheric refraction</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Dispersion of light</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Scattering of light</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Ray Optics</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>What is the focal length of a perfectly flat plane mirror?</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>10 cm</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Infinity</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Thermodynamics</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>The First Law of Thermodynamics stands as a direct consequence of the foundational law of conservation of:</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Wave Motion</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>If the frequency of a periodic wave propagating through a stable, uniform medium is doubled, its corresponding wavelength will:</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Remain unchanged</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Be cut in half</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Quadruple</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Work, Energy &amp; Power</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>The total net work done by a conservative force on an object moving along a complete closed loop path is always:</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Dependent on the path's shape</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Physics - Gravitation</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>The escape velocity of a projectile launched from the surface of the Earth depends explicitly upon:</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>The mass of the launching projectile</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>The mass and radius of the Earth</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>The launch angle of projection</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>The current surface atmospheric temperature</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Chemical Bonding</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Which type of chemical bond is formed via the complete transfer of one or more valence electrons from one atom to another?</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Covalent bond</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Ionic bond</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Coordinate bond</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Metallic bond</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Periodic Table</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Moving sequentially from left to right across a period in the periodic table, the atomic electronegativity generally:</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Increases</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Decreases</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Remains constant</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>First decreases, then increases</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Mole Concept</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>What is the exact mass of one mole of water (H2O) molecules? (Atomic masses: H = 1 u, O = 16 u)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>10 g</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>16 g</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>18 g</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>32 g</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - States of Matter</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Which of the following equations correctly outlines the Ideal Gas Law relationship?</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>PV = nRT</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>P1V1 = P2V2</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>V = kT</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>P = kT</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Chemical Bonding</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>What is the spatial hybridization state of the central carbon atom in a methane (CH4) molecule?</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>sp2</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>sp3</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>dsp2</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Organic Chemistry</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Which of the following functional groups characteristically defines an organic alcohol?</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>-CHO</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>-COOH</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>-OH</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>-CO-</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Electrochemistry</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>An electrochemical device that converts spontaneous chemical energy directly into usable electrical energy is classified as a:</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Electrolytic cell</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Galvanic (Voltaic) cell</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Fuel cell</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Electroplating cell</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Solutions</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>The molarity (M) of a chemical solution is explicitly defined as the number of moles of solute dissolved per:</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Kilogram of solvent</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Liter of solvent</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Liter of total solution</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>100 grams of solution</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Atomic Structure</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>According to the quantum mechanical atomic model, what is the maximum number of electrons that can occupy a single d-subshell?</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry - Chemical Kinetics</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>A chemical catalyst accelerates the overall rate of a reaction primarily by:</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Elevating the system's collision frequency</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Increasing the average kinetic energy of the reactants</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Lowering the required activation energy pathway</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Shifting the position of chemical equilibrium</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>English - Vocabulary</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Choose the word that is closest in meaning (synonym) to: Diligent</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Lazy</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Hardworking</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Careless</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Arrogant</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>English - Vocabulary</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Choose the word that is most opposite in meaning (antonym) to: Benevolent</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Malevolent</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Generous</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Friendly</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>English - Grammar</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Fill in the blank with the correct form of the verb: "Either the teacher or the students ________ responsible for cleaning the classroom laboratory today."</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>was</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>has</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>English - Grammar</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Fill in the blank with the most appropriate preposition: "She has been suffering ________ a severe fever since yesterday morning."</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>with</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>by</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>English - Idioms</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>What is the intended meaning of the idiom "to burn the midnight oil"?</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>To waste fuel resources unnecessarily</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>To work or study diligently late into the night</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>To cause an accidental fire hazard</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>To wake up exceptionally early in the morning</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>English - Grammar</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Identify the grammatically correct sentence from the choices below:</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Me and him went to the campus library yesterday.</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>He and I went to the campus library yesterday.</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Him and me went to the campus library yesterday.</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>He and me went to the campus library yesterday.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>English - Vocabulary</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Select the correct one-word substitution for the phrase: "A person who consistently looks at the bright, favorable side of things."</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Pessimist</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Optimist</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Introvert</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>English - Spellings</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Select the correctly spelled word from the options below:</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Accommodate</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Acomodate</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Accomodate</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Acommodate</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>English - Grammar</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Choose the correct passive voice transformation for the sentence: "The chef prepared a delicious meal."</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>A delicious meal is prepared by the chef.</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>A delicious meal was prepared by the chef.</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>A delicious meal had been prepared by the chef.</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>A delicious meal was preparing by the chef.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>multipleChoice</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>English - Grammar</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Choose the correct indirect speech conversion for the sentence: She said, "I am reading a book."</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>She said that she is reading a book.</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>She said that she was reading a book.</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>She said that I was reading a book.</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>She said that she has been reading a book.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>shortAnswer</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Motivation</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Why do you want to join Noida International University? Explain your motivation and career goals. (100-150 words)</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>150</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -759,21 +3157,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>course</t>
@@ -781,7 +3178,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>test_title</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -814,173 +3211,252 @@
           <t>is_published</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>show_results</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>e.g. B.Tech, BBA, B.Sc</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Test title shown to students</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Number of questions</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Duration in minutes</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Marks per correct answer</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>yes / no</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Marks deducted per wrong answer (0 if none)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>yes / no — is test live?</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>yes / no — show results to students?</t>
-        </is>
-      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>soahs_ug</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>NIU-SAT SOAHS UG Aptitude Test</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>NSAT Question Bank — Template Instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>B.Tech Entrance Exam 2026</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>QUESTIONS SHEET</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>BBA</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>BBA Admission Test 2026</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>• Column A (type): 'multipleChoice' or 'shortAnswer'</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>B.Sc</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>B.Sc General Aptitude Test</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>• Column B (course): Canonical key — must match the test config (e.g. btech, bba, soahs_ug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>• Column C (topic): Optional topic tag for categorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>• Column D (question_text): The full question text</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>• Columns E-H (options): For MCQ only — the 4 answer options</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>• Column I (correct_option): A, B, C, or D — for MCQ only. Leave blank for short answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>• Column J-K (min/max_words): For short answer only — word count guidance (e.g. 100, 150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>SHORT ANSWER QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>• Short answer questions are NOT scored — they are saved for admissions review</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>• Students see a text box with a live word counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>• Leave options (E-H) and correct_option (I) blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>• Set min_words=100 and max_words=150 for the standard essay question</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>TEST CONFIG SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>• One row per course/test</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>• question_count: Total questions INCLUDING the short answer question</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>• negative_marking: 'yes' or 'no'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>• Negative marks apply ONLY to MCQs (short answers are ungraded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>• is_published: 'yes' makes the test available to students</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>COLOR CODING</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>• Green rows = MCQ questions (scored)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>• Gold rows = Short answer questions (unscored, for review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>SEEDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>• Run: python seed_firestore.py NSAT_QuestionBank.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>• The script reads both sheets and creates Firestore documents</t>
         </is>
       </c>
     </row>
